--- a/final_results/mortgage/Random ForestmultipleIFACS.xlsx
+++ b/final_results/mortgage/Random ForestmultipleIFACS.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IFAC_GL</t>
+          <t>IFAC-GL</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -708,7 +708,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>IFAC_U</t>
+          <t>IFAC-U</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -930,7 +930,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>IFAC_GL</t>
+          <t>IFAC-GL</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -967,7 +967,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>IFAC_U</t>
+          <t>IFAC-U</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IFAC_GL</t>
+          <t>IFAC-GL</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IFAC_U</t>
+          <t>IFAC-U</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IFAC_GL</t>
+          <t>IFAC-GL</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IFAC_U</t>
+          <t>IFAC-U</t>
         </is>
       </c>
       <c r="C29" t="n">
